--- a/docs/MockProject_API_Document.xlsx
+++ b/docs/MockProject_API_Document.xlsx
@@ -287,7 +287,7 @@
   <si>
     <t>search (optional): string - Từ khóa tìm theo tên vật tư hoặc mã vật tư
 category (optional): string - Lọc theo nhóm vật tư
-status (optional): string - Lọc theo trạng thái ACTIVE | INACTIVE | OUT_OF_STOCK | DISCONTINUED</t>
+status (optional): string - Lọc theo trạng thái AVAILABLE | INACTIVE | OUT_OF_STOCK | LOW_STOCK</t>
   </si>
   <si>
     <t>Success (200 OK)
@@ -302,7 +302,7 @@
    "unit": "item",
    "quantityOnHand": 22,
    "reorderThreshold": 5,
-   "status": "ACTIVE",
+   "status": "AVAILABLE",
    "lastUpdatedAt": "2026-07-07T09:30:00+07:00"
   }
  ]
@@ -332,7 +332,7 @@
     "unit": "item",
     "quantityOnHand": 10,
     "reorderThreshold": 3,
-    "status": "ACTIVE"
+    "status": "AVAILABLE"
 }
 </t>
   </si>
@@ -348,7 +348,7 @@
   "unit": "item",
   "quantityOnHand": 10,
   "reorderThreshold": 3,
-  "status": "ACTIVE"
+  "status": "AVAILABLE"
  }
 }
 Error (409 Conflict)
@@ -378,7 +378,7 @@
     "unit": "item",
     "quantityOnHand": 12,
     "reorderThreshold": 4,
-    "status": "ACTIVE"
+    "status": "AVAILABLE"
 }
 </t>
   </si>
@@ -394,7 +394,7 @@
   "unit": "item",
   "quantityOnHand": 12,
   "reorderThreshold": 4,
-  "status": "ACTIVE"
+  "status": "AVAILABLE"
  }
 }
 Error (404 Not Found)
@@ -436,7 +436,7 @@
 {
  "message": "Validation failed.",
  "errors": [
-  "status must be one of ACTIVE, INACTIVE, OUT_OF_STOCK, DISCONTINUED"
+  "status must be one of AVAILABLE, INACTIVE, OUT_OF_STOCK, LOW_STOCK"
  ]
 }
 Error (404 Not Found)
@@ -1162,7 +1162,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1176,7 +1176,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1190,7 +1190,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1204,7 +1204,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1218,7 +1218,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1232,7 +1232,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1246,7 +1246,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1260,7 +1260,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1274,7 +1274,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1288,7 +1288,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1302,7 +1302,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1316,7 +1316,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1330,7 +1330,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1383,7 +1383,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="MockProject_API_Document.xls-style" pivot="0" count="4" xr9:uid="{80776837-BF7D-403C-BD28-DCBB3877D8EF}">
+    <tableStyle name="MockProject_API_Document.xls-style" pivot="0" count="4" xr9:uid="{4F0A6D87-DBDC-4496-A39C-0377D092C056}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -2079,7 +2079,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" sqref="A2:A7 A8:A10 A11:A17"/>
+    <dataValidation allowBlank="1" sqref="A2:A17"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
